--- a/branches/issue-70/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/branches/issue-70/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T15:44:48+00:00</t>
+    <t>2024-12-05T15:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
